--- a/sheets/민요/검수/천안 삼거리 (채보1).xlsx
+++ b/sheets/민요/검수/천안 삼거리 (채보1).xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +131,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2204,8 +2263,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -2216,505 +2279,422 @@
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">천안 삼거리 — 민요채보-1/천안 삼거리.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">천안 삼거리</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">興
 潢
 潢</t>
         </is>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="C3" s="12"/>
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">興
 姑
 無</t>
         </is>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="E3" s="12"/>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 興
 潢</t>
         </is>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="G3" s="12"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="13"/>
+    </row>
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="13"/>
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="13"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="G4" s="13"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="C5" s="13"/>
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">興
 無</t>
         </is>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" s="12"/>
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="G5" s="13"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="13"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="C6" s="14"/>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="G6" s="13"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="13"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="13"/>
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" s="13"/>
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="G7" s="13"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="13"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="13"/>
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="13"/>
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="G8" s="13"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="13"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">古
 無
 仲</t>
         </is>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="12"/>
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" s="13"/>
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="G9" s="13"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="13"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="13"/>
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="13"/>
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="G10" s="13"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="13"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="13"/>
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="E11" s="13"/>
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="G11" s="13"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="13"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" s="13"/>
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E12" s="13"/>
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="G12" s="13"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="13"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
 姑</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" s="13"/>
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 湳</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E13" s="13"/>
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃</t>
         </is>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="G13" s="13"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="13"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="14"/>
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="13"/>
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 黃</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="G14" s="13"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="13"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C15" s="13"/>
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
 無</t>
         </is>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="E15" s="13"/>
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="G15" s="13"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 無</t>
         </is>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C16" s="13"/>
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="E16" s="13"/>
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="G16" s="13"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="13"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C17" s="13"/>
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="E17" s="13"/>
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="G17" s="13"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="13"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="C18" s="14"/>
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="E18" s="14"/>
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="13"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="77"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/천안 삼거리 (채보1).xlsx
+++ b/sheets/민요/검수/천안 삼거리 (채보1).xlsx
@@ -405,7 +405,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -3130,7 +3130,7 @@
       <c r="E8" s="9"/>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>

--- a/sheets/민요/검수/천안 삼거리 (채보1).xlsx
+++ b/sheets/민요/검수/천안 삼거리 (채보1).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2924,58 +2962,58 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">천안 삼거리</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">성화가</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에루화</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">제맛에</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">천안</t>
         </is>
@@ -2983,58 +3021,58 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I4" s="9"/>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C4" s="25"/>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E4" s="25"/>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G4" s="25"/>
+      <c r="H4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C5" s="25"/>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E5" s="25"/>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G5" s="25"/>
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -3042,42 +3080,42 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">났구나</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">좋다</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">계워</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">거리</t>
         </is>
@@ -3085,91 +3123,91 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="C7" s="24"/>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E7" s="24"/>
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="24"/>
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I7" s="8"/>
+      <c r="I7" s="24"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="25"/>
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="25"/>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="25"/>
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 ·</t>
         </is>
       </c>
-      <c r="I8" s="9"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="C9" s="25"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="E9" s="27"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 姑</t>
         </is>
       </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="G9" s="27"/>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -3177,72 +3215,72 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="26"/>
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 △</t>
         </is>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="26"/>
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="26"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="I10" s="10"/>
+      <c r="I10" s="26"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">절거너</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">느</t>
         </is>
@@ -3250,33 +3288,33 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="25"/>
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="25"/>
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="G12" s="25"/>
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">수야</t>
         </is>
@@ -3284,33 +3322,33 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="25"/>
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="25"/>
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 黃</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="G13" s="25"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="I13" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">비들</t>
         </is>
@@ -3318,71 +3356,71 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="26"/>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="26"/>
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 仲</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
+      <c r="I14" s="26"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="C15" s="24"/>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -3390,62 +3428,62 @@
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="C16" s="25"/>
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="E16" s="25"/>
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="G16" s="25"/>
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="I16" s="9"/>
+      <c r="I16" s="25"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="C17" s="25"/>
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="E17" s="25"/>
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="G17" s="25"/>
+      <c r="H17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
@@ -3453,31 +3491,31 @@
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 ·</t>
         </is>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C18" s="26"/>
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="E18" s="26"/>
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="G18" s="26"/>
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I18" s="10"/>
+      <c r="I18" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/천안 삼거리 (채보1).xlsx
+++ b/sheets/민요/검수/천안 삼거리 (채보1).xlsx
@@ -2947,20 +2947,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="I4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="I7" s="24"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -3176,12 +3176,12 @@
       <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-·</t>
+–</t>
         </is>
       </c>
       <c r="I8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="I10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -3286,11 +3286,11 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C12" s="25"/>
@@ -3320,7 +3320,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="23" t="inlineStr">
         <is>
@@ -3426,11 +3426,11 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C16" s="25"/>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="I16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="23" t="inlineStr">
         <is>
@@ -3489,12 +3489,12 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-·</t>
+–</t>
         </is>
       </c>
       <c r="C18" s="26"/>
@@ -3506,13 +3506,13 @@
       <c r="E18" s="26"/>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G18" s="26"/>
       <c r="H18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I18" s="26"/>

--- a/sheets/민요/검수/천안 삼거리 (채보1).xlsx
+++ b/sheets/민요/검수/천안 삼거리 (채보1).xlsx
@@ -2984,7 +2984,9 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">성화가</t>
+          <t xml:space="preserve">성
+화
+가</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
@@ -2994,7 +2996,9 @@
       </c>
       <c r="E3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">에루화</t>
+          <t xml:space="preserve">에
+루
+화</t>
         </is>
       </c>
       <c r="F3" s="21" t="inlineStr">
@@ -3004,7 +3008,9 @@
       </c>
       <c r="G3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">제맛에</t>
+          <t xml:space="preserve">제
+맛
+에</t>
         </is>
       </c>
       <c r="H3" s="23" t="inlineStr">
@@ -3015,7 +3021,8 @@
       </c>
       <c r="I3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">천안</t>
+          <t xml:space="preserve">천
+안</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3094,9 @@
       </c>
       <c r="C6" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">났구나</t>
+          <t xml:space="preserve">났
+구
+나</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -3097,7 +3106,8 @@
       </c>
       <c r="E6" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">좋다</t>
+          <t xml:space="preserve">좋
+다</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -3107,7 +3117,8 @@
       </c>
       <c r="G6" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">계워</t>
+          <t xml:space="preserve">계
+워</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -3117,7 +3128,8 @@
       </c>
       <c r="I6" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">거리</t>
+          <t xml:space="preserve">거
+리</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3284,9 @@
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">절거너</t>
+          <t xml:space="preserve">절
+거
+너</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -3316,7 +3330,8 @@
       </c>
       <c r="I12" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">수야</t>
+          <t xml:space="preserve">수
+야</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3365,8 @@
       </c>
       <c r="I13" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">비들</t>
+          <t xml:space="preserve">비
+들</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/천안 삼거리 (채보1).xlsx
+++ b/sheets/민요/검수/천안 삼거리 (채보1).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,6 +238,21 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2982,7 +3002,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">성
 화
@@ -2994,7 +3014,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에
 루
@@ -3006,7 +3026,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">제
 맛
@@ -3019,7 +3039,7 @@
 姑</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">천
 안</t>
@@ -3033,25 +3053,25 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="30"/>
       <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E4" s="25"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G4" s="25"/>
+      <c r="G4" s="30"/>
       <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I4" s="25"/>
+      <c r="I4" s="30"/>
     </row>
     <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
@@ -3060,26 +3080,26 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C5" s="25"/>
+      <c r="C5" s="30"/>
       <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E5" s="25"/>
+      <c r="E5" s="30"/>
       <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G5" s="25"/>
+      <c r="G5" s="30"/>
       <c r="H5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -3092,7 +3112,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">났
 구
@@ -3104,7 +3124,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">좋
 다</t>
@@ -3115,7 +3135,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">계
 워</t>
@@ -3126,7 +3146,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I6" s="26" t="inlineStr">
+      <c r="I6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">거
 리</t>
@@ -3141,26 +3161,26 @@
 無</t>
         </is>
       </c>
-      <c r="C7" s="24"/>
+      <c r="C7" s="29"/>
       <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E7" s="24"/>
+      <c r="E7" s="29"/>
       <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G7" s="24"/>
+      <c r="G7" s="29"/>
       <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I7" s="24"/>
+      <c r="I7" s="29"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
@@ -3170,28 +3190,28 @@
 無</t>
         </is>
       </c>
-      <c r="C8" s="25"/>
+      <c r="C8" s="30"/>
       <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E8" s="25"/>
+      <c r="E8" s="30"/>
       <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="G8" s="25"/>
+      <c r="G8" s="30"/>
       <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –</t>
         </is>
       </c>
-      <c r="I8" s="25"/>
+      <c r="I8" s="30"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
@@ -3200,26 +3220,26 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C9" s="25"/>
+      <c r="C9" s="30"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E9" s="27"/>
+      <c r="E9" s="32"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 姑</t>
         </is>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="32"/>
       <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I9" s="25" t="inlineStr">
+      <c r="I9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -3232,27 +3252,27 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C10" s="26"/>
+      <c r="C10" s="31"/>
       <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 △</t>
         </is>
       </c>
-      <c r="E10" s="26"/>
+      <c r="E10" s="31"/>
       <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="31"/>
       <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="I10" s="26"/>
+      <c r="I10" s="31"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -3261,7 +3281,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -3271,7 +3291,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -3282,7 +3302,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">절
 거
@@ -3294,7 +3314,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="I11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">느</t>
         </is>
@@ -3307,28 +3327,28 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="25"/>
+      <c r="C12" s="30"/>
       <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="E12" s="25"/>
+      <c r="E12" s="30"/>
       <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G12" s="25"/>
+      <c r="G12" s="30"/>
       <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I12" s="25" t="inlineStr">
+      <c r="I12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">수
 야</t>
@@ -3343,27 +3363,27 @@
 無</t>
         </is>
       </c>
-      <c r="C13" s="25"/>
+      <c r="C13" s="30"/>
       <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E13" s="25"/>
+      <c r="E13" s="30"/>
       <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 黃</t>
         </is>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="30"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="I13" s="27" t="inlineStr">
+      <c r="I13" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">비
 들</t>
@@ -3377,7 +3397,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
@@ -3388,20 +3408,20 @@
 無</t>
         </is>
       </c>
-      <c r="E14" s="26"/>
+      <c r="E14" s="31"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G14" s="26"/>
+      <c r="G14" s="31"/>
       <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 仲</t>
         </is>
       </c>
-      <c r="I14" s="26"/>
+      <c r="I14" s="31"/>
     </row>
     <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
@@ -3410,13 +3430,13 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C15" s="24"/>
+      <c r="C15" s="29"/>
       <c r="D15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
@@ -3426,7 +3446,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G15" s="24" t="inlineStr">
+      <c r="G15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -3436,7 +3456,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I15" s="24" t="inlineStr">
+      <c r="I15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -3449,28 +3469,28 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C16" s="25"/>
+      <c r="C16" s="30"/>
       <c r="D16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="E16" s="25"/>
+      <c r="E16" s="30"/>
       <c r="F16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="G16" s="25"/>
+      <c r="G16" s="30"/>
       <c r="H16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="I16" s="25"/>
+      <c r="I16" s="30"/>
     </row>
     <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
@@ -3480,26 +3500,26 @@
 無</t>
         </is>
       </c>
-      <c r="C17" s="25"/>
+      <c r="C17" s="30"/>
       <c r="D17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="E17" s="25"/>
+      <c r="E17" s="30"/>
       <c r="F17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G17" s="25"/>
+      <c r="G17" s="30"/>
       <c r="H17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I17" s="25" t="inlineStr">
+      <c r="I17" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
@@ -3513,25 +3533,25 @@
 –</t>
         </is>
       </c>
-      <c r="C18" s="26"/>
+      <c r="C18" s="31"/>
       <c r="D18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E18" s="26"/>
+      <c r="E18" s="31"/>
       <c r="F18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G18" s="26"/>
+      <c r="G18" s="31"/>
       <c r="H18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I18" s="26"/>
+      <c r="I18" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/천안 삼거리 (채보1).xlsx
+++ b/sheets/민요/검수/천안 삼거리 (채보1).xlsx
@@ -338,7 +338,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
     </row>
@@ -374,7 +374,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고 54%, 박자 근사</t>
+          <t xml:space="preserve">비고 58%, 박자 근사</t>
         </is>
       </c>
     </row>
@@ -402,7 +402,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 16번호 양식이지만 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개에 율명 3개씩(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8(근사). 인쇄 1열은 비어 있어 인쇄 2·3·4열을 줄1~3으로 함(5~8열 빈칸). 오른쪽 여백에 "천안삼거리 굿거리". 가사는 각 율명 줄 오른쪽 칸. 한 큰 칸에 가사가 위·아래로 나뉜 곳(흥…응)은 붙여 씀. 하단 "- 196 -"은 양식 번호.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 16번호 양식이지만 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개에 율명 3개씩(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8(근사). 인쇄 1열은 비어 있어 인쇄 2·3·4열을 줄1~3으로 함(5~8열 빈칸). 오른쪽 여백에 "천안삼거리 굿거리". 가사는 각 율명 줄 오른쪽 칸. 한 큰 칸에 가사가 위·아래로 나뉜 곳(흥…응)은 붙여 씀. 하단 "- 196 -"은 양식 번호. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -756,24 +756,28 @@
       <c r="F6" s="2">
         <v>2</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑|無姑|潢</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-無姑
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|無南|潢</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無南
 潢</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">능수야</t>
         </is>
       </c>
-      <c r="J6" s="4"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南/姑?</t>
+        </is>
+      </c>
       <c r="K6" s="2"/>
     </row>
     <row r="7">
@@ -1139,13 +1143,13 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|–汰|潢</t>
+          <t xml:space="preserve">仲|–㴌|潢</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-–汰
+–㴌
 潢</t>
         </is>
       </c>
@@ -1184,13 +1188,13 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|–汰|潢無</t>
+          <t xml:space="preserve">潢|–㴌|潢無</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–汰
+–㴌
 潢無</t>
         </is>
       </c>
@@ -1815,14 +1819,14 @@
 어</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-無姑
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無南
 潢</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">능
 수
@@ -1849,7 +1853,7 @@
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-–汰
+–㴌
 潢</t>
         </is>
       </c>
@@ -1893,7 +1897,7 @@
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–汰
+–㴌
 潢無</t>
         </is>
       </c>
